--- a/Results/Consensus/CC/Supplement/Chisq_tests.xlsx
+++ b/Results/Consensus/CC/Supplement/Chisq_tests.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t xml:space="preserve">Comparison</t>
   </si>
@@ -29,10 +29,10 @@
     <t xml:space="preserve">Vital status vs CC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999999999999994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82962152480127e-29</t>
+    <t xml:space="preserve">0.999999999999992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11735324592793e-28</t>
   </si>
   <si>
     <t xml:space="preserve">0</t>
@@ -41,52 +41,49 @@
     <t xml:space="preserve">Ethnicity vs CC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999999999999995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44888135652566e-29</t>
+    <t xml:space="preserve">0.999999999999999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65649404804653e-30</t>
   </si>
   <si>
     <t xml:space="preserve">Race vs CC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49541979902404e-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.142703298027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.199</t>
+    <t xml:space="preserve">7.58987547797536e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4736251811788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.196</t>
   </si>
   <si>
     <t xml:space="preserve">Lymph node status vs CC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.999999999999999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53598437773786e-31</t>
+    <t xml:space="preserve">1.00580649365164e-28</t>
   </si>
   <si>
     <t xml:space="preserve">Histology vs CC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00784066559269e-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6652896181873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344</t>
+    <t xml:space="preserve">6.26387185915341e-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.6772673601045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346</t>
   </si>
   <si>
     <t xml:space="preserve">Menopausal status vs CC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0429561841424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15284846024776</t>
+    <t xml:space="preserve">0.0418617323549828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21018780079514</t>
   </si>
   <si>
     <t xml:space="preserve">0.095</t>
@@ -95,55 +92,55 @@
     <t xml:space="preserve">PR status vs CC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23989286233504e-56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.442469834131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.656</t>
+    <t xml:space="preserve">5.97326328395952e-55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">249.709773445757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651</t>
   </si>
   <si>
     <t xml:space="preserve">ER status vs CC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44039645163658e-76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.916656191058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768</t>
+    <t xml:space="preserve">1.85088385257063e-75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">337.876298674877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763</t>
   </si>
   <si>
     <t xml:space="preserve">HER2 status vs CC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28801588897424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76472554189983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.039</t>
+    <t xml:space="preserve">0.414133664248806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85742566869192</t>
   </si>
   <si>
     <t xml:space="preserve">Metastasis vs CC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02129665263397e-31</t>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67913449601358e-31</t>
   </si>
   <si>
     <t xml:space="preserve">Stage vs CC cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0192698555386722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91871734871614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106</t>
+    <t xml:space="preserve">0.0305764210129069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90532986296027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.098</t>
   </si>
 </sst>
 </file>
@@ -533,10 +530,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
         <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -544,83 +541,83 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
         <v>26</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>27</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
         <v>30</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>31</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
         <v>34</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>35</v>
       </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
         <v>38</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -628,16 +625,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s">
         <v>40</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>41</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>42</v>
-      </c>
-      <c r="D12" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
